--- a/reports/data_dictionary.xlsx
+++ b/reports/data_dictionary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,7 +745,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COST_OVERRUN_PCT</t>
+          <t>PROJECT_ID</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PROGRESS_GAP</t>
+          <t>COST_OVERRUN_PCT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCHEDULE_CHANGE_DAYS</t>
+          <t>PROGRESS_GAP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -787,6 +787,22 @@
         </is>
       </c>
       <c r="D23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SCHEDULE_CHANGE_DAYS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>1382</v>
       </c>
     </row>
